--- a/docentes/Velasco Sánchez David - Estadisticos 20212.xlsx
+++ b/docentes/Velasco Sánchez David - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="220">
   <si>
     <t>Mat</t>
   </si>
@@ -85,193 +85,325 @@
     <t>ALVAREZ</t>
   </si>
   <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>CLEMENTE</t>
+  </si>
+  <si>
+    <t>ENCARNACION</t>
+  </si>
+  <si>
+    <t>ELIZALDE</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>RIOS</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>BALDERAS</t>
+  </si>
+  <si>
+    <t>BONOLA</t>
+  </si>
+  <si>
+    <t>COYOHUA</t>
+  </si>
+  <si>
+    <t>GAMEZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>TEHUINTLE</t>
+  </si>
+  <si>
+    <t>ZUÑIGA</t>
+  </si>
+  <si>
+    <t>ALEJO</t>
+  </si>
+  <si>
+    <t>CESPEDES</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>ESTRADA</t>
+  </si>
+  <si>
+    <t>GASPAR</t>
+  </si>
+  <si>
+    <t>LADINO</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>REYNOSO</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>FLORENCIO</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
+    <t>TAPIA</t>
+  </si>
+  <si>
+    <t>TOCOHUA</t>
+  </si>
+  <si>
     <t>ARIAS</t>
   </si>
   <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
     <t>BALDEZ</t>
   </si>
   <si>
-    <t>CLEMENTE</t>
-  </si>
-  <si>
-    <t>ENCARNACION</t>
-  </si>
-  <si>
-    <t>ELIZALDE</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
     <t>RAMIREZ</t>
   </si>
   <si>
-    <t>RIOS</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
     <t>ROMAN</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
     <t>SEGURA</t>
   </si>
   <si>
     <t>TZANAHUA</t>
   </si>
   <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>ALEJO</t>
+    <t>AYOCTLE</t>
+  </si>
+  <si>
+    <t>CHICO</t>
+  </si>
+  <si>
+    <t>CABRERA</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MACARIO</t>
+  </si>
+  <si>
+    <t>MARQUEZ</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>OLTEHUA</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
   </si>
   <si>
     <t>CARDENAS</t>
   </si>
   <si>
-    <t>CESPEDES</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>ESTRADA</t>
-  </si>
-  <si>
-    <t>GASPAR</t>
-  </si>
-  <si>
     <t>GUTIERREZ</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>LADINO</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>REYNOSO</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
     <t>AGUILAR</t>
   </si>
   <si>
     <t>CASTILLO</t>
   </si>
   <si>
-    <t>FLORENCIO</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
     <t>JUAN</t>
   </si>
   <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>SUAREZ</t>
-  </si>
-  <si>
-    <t>TAPIA</t>
-  </si>
-  <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
-    <t>TOCOHUA</t>
-  </si>
-  <si>
     <t>MORAN</t>
   </si>
   <si>
     <t>VENTURA</t>
   </si>
   <si>
+    <t>PALAGOT</t>
+  </si>
+  <si>
+    <t>BELTRAN</t>
+  </si>
+  <si>
+    <t>SORIANO</t>
+  </si>
+  <si>
+    <t>MELENDEZ</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
+    <t>CHAVEZ</t>
+  </si>
+  <si>
+    <t>SIERRA</t>
+  </si>
+  <si>
+    <t>NUBE</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>SILVERIO</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>YOPIHUA</t>
+  </si>
+  <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>CASTAÑEDA</t>
+  </si>
+  <si>
+    <t>HUESCA</t>
+  </si>
+  <si>
+    <t>ANDRADE</t>
+  </si>
+  <si>
+    <t>ALCARAZ</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>LLAVE</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>BERNABE</t>
+  </si>
+  <si>
+    <t>MIRON</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>ANGUIANO</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>BERISTAIN</t>
+  </si>
+  <si>
     <t>IXTACUA</t>
   </si>
   <si>
-    <t>PALAGOT</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>BELTRAN</t>
-  </si>
-  <si>
-    <t>MELENDEZ</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
     <t>YEPEZ</t>
   </si>
   <si>
-    <t>CHAVEZ</t>
-  </si>
-  <si>
     <t>MELLADO</t>
   </si>
   <si>
-    <t>CHICO</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>CASTAÑEDA</t>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>BERUDEZ</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>NIEVES</t>
+  </si>
+  <si>
+    <t>ONOFRE</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>CARTEÑO</t>
   </si>
   <si>
     <t>CELICEO</t>
@@ -280,87 +412,168 @@
     <t>CALPULALPAN</t>
   </si>
   <si>
-    <t>HUESCA</t>
-  </si>
-  <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
-    <t>ALCARAZ</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>LLAVE</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
     <t>TEZOCO</t>
   </si>
   <si>
-    <t>BERNABE</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>MIRON</t>
-  </si>
-  <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>ANGUIANO</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
     <t>TETLA</t>
   </si>
   <si>
-    <t>BERISTAIN</t>
-  </si>
-  <si>
     <t>JOSE MANUEL</t>
   </si>
   <si>
+    <t>ALEX SAUL</t>
+  </si>
+  <si>
+    <t>IVAN</t>
+  </si>
+  <si>
+    <t>JESSICA</t>
+  </si>
+  <si>
+    <t>ALBERTO</t>
+  </si>
+  <si>
+    <t>EMMANUEL</t>
+  </si>
+  <si>
+    <t>HAZIEL</t>
+  </si>
+  <si>
+    <t>JESUS</t>
+  </si>
+  <si>
+    <t>SAUL ALEJANDRO</t>
+  </si>
+  <si>
+    <t>LOGAN ZURIEL</t>
+  </si>
+  <si>
+    <t>YAIR ANTONIO</t>
+  </si>
+  <si>
+    <t>JOSE AUGUSTO</t>
+  </si>
+  <si>
+    <t>ISRAEL</t>
+  </si>
+  <si>
+    <t>ANUAR ANTONIO</t>
+  </si>
+  <si>
+    <t>ERICK ORLANDO</t>
+  </si>
+  <si>
+    <t>LUIS ALEJANDRO</t>
+  </si>
+  <si>
+    <t>IAN ISSAID</t>
+  </si>
+  <si>
+    <t>MICHELL</t>
+  </si>
+  <si>
+    <t>MICAELA</t>
+  </si>
+  <si>
+    <t>MARCO ANTONIO</t>
+  </si>
+  <si>
+    <t>MIGUEL ANGEL</t>
+  </si>
+  <si>
+    <t>FRANCISCO EMMANUEL</t>
+  </si>
+  <si>
+    <t>YAMILET</t>
+  </si>
+  <si>
+    <t>KAROL</t>
+  </si>
+  <si>
+    <t>MARLENE</t>
+  </si>
+  <si>
+    <t>RAUL ALEJANDRO</t>
+  </si>
+  <si>
+    <t>ERICK MANUEL</t>
+  </si>
+  <si>
+    <t>IRVING YAHIR</t>
+  </si>
+  <si>
+    <t>BRAULIO VADIR</t>
+  </si>
+  <si>
+    <t>VIANEY</t>
+  </si>
+  <si>
+    <t>ZURISADAI</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>ALEXANDER</t>
+  </si>
+  <si>
+    <t>RENZO JHOVANI</t>
+  </si>
+  <si>
+    <t>NADYA GUADALUPE</t>
+  </si>
+  <si>
+    <t>ANGEL EDUARDO</t>
+  </si>
+  <si>
+    <t>YESUA ISIDRO</t>
+  </si>
+  <si>
+    <t>JOSE JAZAEL</t>
+  </si>
+  <si>
+    <t>ELEAZAR RIGOBERTO</t>
+  </si>
+  <si>
+    <t>JESUS ENRIQUE</t>
+  </si>
+  <si>
+    <t>JUAN LUIS</t>
+  </si>
+  <si>
+    <t>EDUARDO</t>
+  </si>
+  <si>
+    <t>YAEL</t>
+  </si>
+  <si>
+    <t>ARIAN ALEXIS</t>
+  </si>
+  <si>
+    <t>JOSUE</t>
+  </si>
+  <si>
+    <t>YARITZI</t>
+  </si>
+  <si>
+    <t>ROMARIO ALDAIR</t>
+  </si>
+  <si>
+    <t>MARIA ISABEL</t>
+  </si>
+  <si>
+    <t>ADOLFO</t>
+  </si>
+  <si>
     <t>CARLOS ALBERTO</t>
   </si>
   <si>
-    <t>ALEX SAUL</t>
-  </si>
-  <si>
-    <t>IVAN</t>
-  </si>
-  <si>
-    <t>JESSICA</t>
-  </si>
-  <si>
-    <t>ALBERTO</t>
-  </si>
-  <si>
     <t>GIOVANNA</t>
   </si>
   <si>
-    <t>SAUL ALEJANDRO</t>
-  </si>
-  <si>
-    <t>LOGAN ZURIEL</t>
-  </si>
-  <si>
-    <t>YAIR ANTONIO</t>
-  </si>
-  <si>
     <t>HUGO</t>
   </si>
   <si>
@@ -370,21 +583,12 @@
     <t>JAIR</t>
   </si>
   <si>
-    <t>JOSE AUGUSTO</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
-  </si>
-  <si>
     <t>NATANAEL</t>
   </si>
   <si>
     <t>DIANA AMEYALLI</t>
   </si>
   <si>
-    <t>ANUAR ANTONIO</t>
-  </si>
-  <si>
     <t>GAEL</t>
   </si>
   <si>
@@ -397,57 +601,69 @@
     <t>JOCELYN BERENICE</t>
   </si>
   <si>
-    <t>ERICK ORLANDO</t>
-  </si>
-  <si>
-    <t>RAUL ALEJANDRO</t>
+    <t>KARLA</t>
+  </si>
+  <si>
+    <t>EMMA NOHEMI</t>
+  </si>
+  <si>
+    <t>MAYTE DOLORES</t>
+  </si>
+  <si>
+    <t>AYELEN</t>
+  </si>
+  <si>
+    <t>KARIME GUADALUPE</t>
+  </si>
+  <si>
+    <t>JUAN CARLOS</t>
+  </si>
+  <si>
+    <t>MARIANA JOSELIN</t>
+  </si>
+  <si>
+    <t>CINTHIA</t>
+  </si>
+  <si>
+    <t>JUAN MANUEL</t>
+  </si>
+  <si>
+    <t>MARTHA</t>
+  </si>
+  <si>
+    <t>YULIANA</t>
+  </si>
+  <si>
+    <t>DIEGO MIGUEL</t>
+  </si>
+  <si>
+    <t>JAXIRY JAZMIN</t>
+  </si>
+  <si>
+    <t>KATHERINE AZUL</t>
+  </si>
+  <si>
+    <t>LIZETH</t>
+  </si>
+  <si>
+    <t>DANNA ARLETTE</t>
+  </si>
+  <si>
+    <t>RUTH</t>
+  </si>
+  <si>
+    <t>ESTEFANIA</t>
   </si>
   <si>
     <t>JOSE LUIS</t>
   </si>
   <si>
-    <t>ERICK MANUEL</t>
-  </si>
-  <si>
-    <t>IRVING YAHIR</t>
-  </si>
-  <si>
-    <t>BRAULIO VADIR</t>
-  </si>
-  <si>
-    <t>VIANEY</t>
-  </si>
-  <si>
     <t>PAOLA</t>
   </si>
   <si>
     <t>YARELY JACQUELINE</t>
   </si>
   <si>
-    <t>ZURISADAI</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>ALEXANDER</t>
-  </si>
-  <si>
-    <t>RENZO JHOVANI</t>
-  </si>
-  <si>
-    <t>NADYA GUADALUPE</t>
-  </si>
-  <si>
-    <t>ANGEL EDUARDO</t>
-  </si>
-  <si>
-    <t>YESUA ISIDRO</t>
-  </si>
-  <si>
-    <t>JOSE JAZAEL</t>
-  </si>
-  <si>
     <t>JOSE ANTONIO</t>
   </si>
   <si>
@@ -457,49 +673,10 @@
     <t>BRANDON</t>
   </si>
   <si>
-    <t>JESUS ENRIQUE</t>
-  </si>
-  <si>
-    <t>JUAN LUIS</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL</t>
-  </si>
-  <si>
-    <t>EMMANUEL</t>
-  </si>
-  <si>
     <t>OSWALDO ENRIQUE</t>
   </si>
   <si>
-    <t>EDUARDO</t>
-  </si>
-  <si>
-    <t>YAEL</t>
-  </si>
-  <si>
-    <t>ARIAN ALEXIS</t>
-  </si>
-  <si>
-    <t>JOSUE</t>
-  </si>
-  <si>
-    <t>YARITZI</t>
-  </si>
-  <si>
-    <t>ROMARIO ALDAIR</t>
-  </si>
-  <si>
-    <t>YAMILET</t>
-  </si>
-  <si>
-    <t>MARIA ISABEL</t>
-  </si>
-  <si>
     <t>JOSUE GILBERTO</t>
-  </si>
-  <si>
-    <t>ADOLFO</t>
   </si>
 </sst>
 </file>
@@ -1319,7 +1496,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:G92"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1357,10 +1534,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="D2" t="s">
-        <v>104</v>
+        <v>134</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -1374,16 +1551,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920005</v>
+        <v>19330051920004</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>47</v>
+        <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -1397,16 +1574,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920004</v>
+        <v>19330051920008</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>106</v>
+        <v>136</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -1420,16 +1597,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920006</v>
+        <v>19330051920016</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="D5" t="s">
-        <v>23</v>
+        <v>137</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -1443,16 +1620,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920008</v>
+        <v>19330051920015</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="D6" t="s">
-        <v>107</v>
+        <v>138</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -1466,16 +1643,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920016</v>
+        <v>19330051920012</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="D7" t="s">
-        <v>108</v>
+        <v>139</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -1489,16 +1666,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920015</v>
+        <v>19330051920011</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="D8" t="s">
-        <v>109</v>
+        <v>140</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -1512,16 +1689,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920009</v>
+        <v>19330051920010</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>57</v>
+        <v>92</v>
       </c>
       <c r="D9" t="s">
-        <v>110</v>
+        <v>141</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -1538,13 +1715,13 @@
         <v>19330051920017</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="D10" t="s">
-        <v>111</v>
+        <v>142</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -1561,13 +1738,13 @@
         <v>19330051920018</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="D11" t="s">
-        <v>112</v>
+        <v>143</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -1584,13 +1761,13 @@
         <v>18330051920168</v>
       </c>
       <c r="B12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" t="s">
         <v>31</v>
       </c>
-      <c r="C12" t="s">
-        <v>34</v>
-      </c>
       <c r="D12" t="s">
-        <v>113</v>
+        <v>144</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
@@ -1604,16 +1781,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>19330051920020</v>
+        <v>19330051920023</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C13" t="s">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="D13" t="s">
-        <v>114</v>
+        <v>145</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
@@ -1627,16 +1804,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>19330051920022</v>
+        <v>19330051920026</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C14" t="s">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="D14" t="s">
-        <v>115</v>
+        <v>146</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
@@ -1650,16 +1827,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>19330051920021</v>
+        <v>19330051920027</v>
       </c>
       <c r="B15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C15" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D15" t="s">
-        <v>116</v>
+        <v>147</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
@@ -1673,16 +1850,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>19330051920023</v>
+        <v>19330051920038</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C16" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="D16" t="s">
-        <v>117</v>
+        <v>148</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
@@ -1696,22 +1873,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>19330051920026</v>
+        <v>19330051920149</v>
       </c>
       <c r="B17" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C17" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="D17" t="s">
-        <v>118</v>
+        <v>149</v>
       </c>
       <c r="E17" t="s">
         <v>9</v>
       </c>
       <c r="F17" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G17">
         <v>2</v>
@@ -1719,22 +1896,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>18330061460390</v>
+        <v>19330051920150</v>
       </c>
       <c r="B18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C18" t="s">
-        <v>55</v>
+        <v>97</v>
       </c>
       <c r="D18" t="s">
-        <v>119</v>
+        <v>150</v>
       </c>
       <c r="E18" t="s">
         <v>9</v>
       </c>
       <c r="F18" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G18">
         <v>2</v>
@@ -1742,22 +1919,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>19330051920025</v>
+        <v>19330051920154</v>
       </c>
       <c r="B19" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C19" t="s">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="D19" t="s">
-        <v>120</v>
+        <v>151</v>
       </c>
       <c r="E19" t="s">
         <v>9</v>
       </c>
       <c r="F19" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G19">
         <v>2</v>
@@ -1765,22 +1942,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>19330051920027</v>
+        <v>19330051920158</v>
       </c>
       <c r="B20" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C20" t="s">
-        <v>47</v>
+        <v>99</v>
       </c>
       <c r="D20" t="s">
-        <v>121</v>
+        <v>152</v>
       </c>
       <c r="E20" t="s">
         <v>9</v>
       </c>
       <c r="F20" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G20">
         <v>2</v>
@@ -1788,22 +1965,22 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>19330051920029</v>
+        <v>19330051920159</v>
       </c>
       <c r="B21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C21" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D21" t="s">
-        <v>122</v>
+        <v>153</v>
       </c>
       <c r="E21" t="s">
         <v>9</v>
       </c>
       <c r="F21" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G21">
         <v>2</v>
@@ -1811,22 +1988,22 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>19330051920030</v>
+        <v>19330051920162</v>
       </c>
       <c r="B22" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C22" t="s">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="D22" t="s">
-        <v>123</v>
+        <v>154</v>
       </c>
       <c r="E22" t="s">
         <v>9</v>
       </c>
       <c r="F22" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G22">
         <v>2</v>
@@ -1834,22 +2011,22 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>19330051920031</v>
+        <v>19330051920155</v>
       </c>
       <c r="B23" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="C23" t="s">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="D23" t="s">
-        <v>124</v>
+        <v>155</v>
       </c>
       <c r="E23" t="s">
         <v>9</v>
       </c>
       <c r="F23" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G23">
         <v>2</v>
@@ -1857,22 +2034,22 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>19330051920035</v>
+        <v>19330051920178</v>
       </c>
       <c r="B24" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C24" t="s">
-        <v>36</v>
+        <v>101</v>
       </c>
       <c r="D24" t="s">
-        <v>125</v>
+        <v>156</v>
       </c>
       <c r="E24" t="s">
         <v>9</v>
       </c>
       <c r="F24" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G24">
         <v>2</v>
@@ -1880,22 +2057,22 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>19330051920038</v>
+        <v>19330051920181</v>
       </c>
       <c r="B25" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C25" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="D25" t="s">
-        <v>126</v>
+        <v>157</v>
       </c>
       <c r="E25" t="s">
         <v>9</v>
       </c>
       <c r="F25" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G25">
         <v>2</v>
@@ -1903,22 +2080,22 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>19330051920223</v>
+        <v>19330051920183</v>
       </c>
       <c r="B26" t="s">
         <v>40</v>
       </c>
       <c r="C26" t="s">
-        <v>82</v>
+        <v>22</v>
       </c>
       <c r="D26" t="s">
-        <v>127</v>
+        <v>158</v>
       </c>
       <c r="E26" t="s">
         <v>9</v>
       </c>
       <c r="F26" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G26">
         <v>2</v>
@@ -1926,16 +2103,16 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>19330051920430</v>
+        <v>19330051920223</v>
       </c>
       <c r="B27" t="s">
         <v>41</v>
       </c>
       <c r="C27" t="s">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="D27" t="s">
-        <v>128</v>
+        <v>159</v>
       </c>
       <c r="E27" t="s">
         <v>9</v>
@@ -1955,10 +2132,10 @@
         <v>42</v>
       </c>
       <c r="C28" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="D28" t="s">
-        <v>129</v>
+        <v>160</v>
       </c>
       <c r="E28" t="s">
         <v>9</v>
@@ -1978,10 +2155,10 @@
         <v>43</v>
       </c>
       <c r="C29" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D29" t="s">
-        <v>130</v>
+        <v>161</v>
       </c>
       <c r="E29" t="s">
         <v>9</v>
@@ -2001,10 +2178,10 @@
         <v>44</v>
       </c>
       <c r="C30" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="D30" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="E30" t="s">
         <v>9</v>
@@ -2024,10 +2201,10 @@
         <v>45</v>
       </c>
       <c r="C31" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="D31" t="s">
-        <v>132</v>
+        <v>163</v>
       </c>
       <c r="E31" t="s">
         <v>9</v>
@@ -2041,16 +2218,16 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>19330051920234</v>
+        <v>19330051920236</v>
       </c>
       <c r="B32" t="s">
         <v>46</v>
       </c>
       <c r="C32" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D32" t="s">
-        <v>133</v>
+        <v>164</v>
       </c>
       <c r="E32" t="s">
         <v>9</v>
@@ -2064,16 +2241,16 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>19330051920429</v>
+        <v>19330051920228</v>
       </c>
       <c r="B33" t="s">
         <v>47</v>
       </c>
       <c r="C33" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="D33" t="s">
-        <v>134</v>
+        <v>165</v>
       </c>
       <c r="E33" t="s">
         <v>9</v>
@@ -2087,16 +2264,16 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>19330051920236</v>
+        <v>19330051420227</v>
       </c>
       <c r="B34" t="s">
         <v>48</v>
       </c>
       <c r="C34" t="s">
-        <v>47</v>
+        <v>107</v>
       </c>
       <c r="D34" t="s">
-        <v>135</v>
+        <v>166</v>
       </c>
       <c r="E34" t="s">
         <v>9</v>
@@ -2110,16 +2287,16 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>19330051920228</v>
+        <v>19330051920404</v>
       </c>
       <c r="B35" t="s">
         <v>49</v>
       </c>
       <c r="C35" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="D35" t="s">
-        <v>136</v>
+        <v>167</v>
       </c>
       <c r="E35" t="s">
         <v>9</v>
@@ -2133,16 +2310,16 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>19330051420227</v>
+        <v>19330051920239</v>
       </c>
       <c r="B36" t="s">
         <v>50</v>
       </c>
       <c r="C36" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="D36" t="s">
-        <v>137</v>
+        <v>168</v>
       </c>
       <c r="E36" t="s">
         <v>9</v>
@@ -2156,16 +2333,16 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>19330051920404</v>
+        <v>19330051920242</v>
       </c>
       <c r="B37" t="s">
         <v>51</v>
       </c>
       <c r="C37" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="D37" t="s">
-        <v>138</v>
+        <v>169</v>
       </c>
       <c r="E37" t="s">
         <v>9</v>
@@ -2179,16 +2356,16 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>19330051920239</v>
+        <v>19330051920245</v>
       </c>
       <c r="B38" t="s">
         <v>52</v>
       </c>
       <c r="C38" t="s">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="D38" t="s">
-        <v>139</v>
+        <v>170</v>
       </c>
       <c r="E38" t="s">
         <v>9</v>
@@ -2202,22 +2379,22 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>19330051920242</v>
+        <v>19330051920085</v>
       </c>
       <c r="B39" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="C39" t="s">
-        <v>47</v>
+        <v>111</v>
       </c>
       <c r="D39" t="s">
-        <v>140</v>
+        <v>171</v>
       </c>
       <c r="E39" t="s">
         <v>9</v>
       </c>
       <c r="F39" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G39">
         <v>2</v>
@@ -2225,22 +2402,22 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
-        <v>19330051920245</v>
+        <v>19330051920092</v>
       </c>
       <c r="B40" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="C40" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D40" t="s">
-        <v>141</v>
+        <v>172</v>
       </c>
       <c r="E40" t="s">
         <v>9</v>
       </c>
       <c r="F40" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G40">
         <v>2</v>
@@ -2248,16 +2425,16 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41">
-        <v>19330051920085</v>
+        <v>19330051920097</v>
       </c>
       <c r="B41" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="C41" t="s">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="D41" t="s">
-        <v>142</v>
+        <v>173</v>
       </c>
       <c r="E41" t="s">
         <v>9</v>
@@ -2271,16 +2448,16 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42">
-        <v>19330051920084</v>
+        <v>19330051920100</v>
       </c>
       <c r="B42" t="s">
         <v>54</v>
       </c>
       <c r="C42" t="s">
-        <v>93</v>
+        <v>51</v>
       </c>
       <c r="D42" t="s">
-        <v>143</v>
+        <v>174</v>
       </c>
       <c r="E42" t="s">
         <v>9</v>
@@ -2294,16 +2471,16 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43">
-        <v>19330051920090</v>
+        <v>19330051920102</v>
       </c>
       <c r="B43" t="s">
         <v>55</v>
       </c>
       <c r="C43" t="s">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="D43" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="E43" t="s">
         <v>9</v>
@@ -2317,16 +2494,16 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44">
-        <v>19330051920089</v>
+        <v>19330051920106</v>
       </c>
       <c r="B44" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C44" t="s">
-        <v>63</v>
+        <v>113</v>
       </c>
       <c r="D44" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="E44" t="s">
         <v>9</v>
@@ -2340,16 +2517,16 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45">
-        <v>19330051920097</v>
+        <v>19330051920109</v>
       </c>
       <c r="B45" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C45" t="s">
-        <v>94</v>
+        <v>54</v>
       </c>
       <c r="D45" t="s">
-        <v>146</v>
+        <v>175</v>
       </c>
       <c r="E45" t="s">
         <v>9</v>
@@ -2363,16 +2540,16 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46">
-        <v>19330051920100</v>
+        <v>19330051920110</v>
       </c>
       <c r="B46" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="C46" t="s">
-        <v>36</v>
+        <v>114</v>
       </c>
       <c r="D46" t="s">
-        <v>147</v>
+        <v>176</v>
       </c>
       <c r="E46" t="s">
         <v>9</v>
@@ -2386,16 +2563,16 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47">
-        <v>19330051920102</v>
+        <v>19330051920001</v>
       </c>
       <c r="B47" t="s">
         <v>58</v>
       </c>
       <c r="C47" t="s">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="D47" t="s">
-        <v>148</v>
+        <v>177</v>
       </c>
       <c r="E47" t="s">
         <v>9</v>
@@ -2409,16 +2586,16 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48">
-        <v>19330051920106</v>
+        <v>19330051920116</v>
       </c>
       <c r="B48" t="s">
         <v>59</v>
       </c>
       <c r="C48" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D48" t="s">
-        <v>149</v>
+        <v>178</v>
       </c>
       <c r="E48" t="s">
         <v>9</v>
@@ -2432,16 +2609,16 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49">
-        <v>19330051920107</v>
+        <v>19330051920117</v>
       </c>
       <c r="B49" t="s">
         <v>60</v>
       </c>
       <c r="C49" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="D49" t="s">
-        <v>150</v>
+        <v>179</v>
       </c>
       <c r="E49" t="s">
         <v>9</v>
@@ -2455,16 +2632,16 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50">
-        <v>19330051920109</v>
+        <v>19330051920118</v>
       </c>
       <c r="B50" t="s">
         <v>61</v>
       </c>
       <c r="C50" t="s">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="D50" t="s">
-        <v>151</v>
+        <v>180</v>
       </c>
       <c r="E50" t="s">
         <v>9</v>
@@ -2478,16 +2655,16 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51">
-        <v>19330051920110</v>
+        <v>19330051920119</v>
       </c>
       <c r="B51" t="s">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="C51" t="s">
-        <v>98</v>
+        <v>26</v>
       </c>
       <c r="D51" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E51" t="s">
         <v>9</v>
@@ -2501,16 +2678,16 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52">
-        <v>19330051920001</v>
+        <v>19330051920120</v>
       </c>
       <c r="B52" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C52" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="D52" t="s">
-        <v>153</v>
+        <v>181</v>
       </c>
       <c r="E52" t="s">
         <v>9</v>
@@ -2524,16 +2701,16 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53">
-        <v>19330051920116</v>
+        <v>19330051920122</v>
       </c>
       <c r="B53" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C53" t="s">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="D53" t="s">
-        <v>154</v>
+        <v>182</v>
       </c>
       <c r="E53" t="s">
         <v>9</v>
@@ -2547,140 +2724,899 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54">
-        <v>19330051920117</v>
+        <v>19330051920005</v>
       </c>
       <c r="B54" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C54" t="s">
         <v>83</v>
       </c>
       <c r="D54" t="s">
-        <v>155</v>
+        <v>183</v>
       </c>
       <c r="E54" t="s">
         <v>9</v>
       </c>
       <c r="F54" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G54">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55">
-        <v>19330051920118</v>
+        <v>19330051920006</v>
       </c>
       <c r="B55" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C55" t="s">
-        <v>47</v>
+        <v>119</v>
       </c>
       <c r="D55" t="s">
-        <v>156</v>
+        <v>22</v>
       </c>
       <c r="E55" t="s">
         <v>9</v>
       </c>
       <c r="F55" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G55">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56">
-        <v>19330051920119</v>
+        <v>19330051920009</v>
       </c>
       <c r="B56" t="s">
-        <v>66</v>
+        <v>26</v>
       </c>
       <c r="C56" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="D56" t="s">
-        <v>157</v>
+        <v>184</v>
       </c>
       <c r="E56" t="s">
         <v>9</v>
       </c>
       <c r="F56" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G56">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:7">
       <c r="A57">
-        <v>19330051920120</v>
+        <v>19330051920020</v>
       </c>
       <c r="B57" t="s">
         <v>67</v>
       </c>
       <c r="C57" t="s">
-        <v>101</v>
+        <v>51</v>
       </c>
       <c r="D57" t="s">
-        <v>158</v>
+        <v>185</v>
       </c>
       <c r="E57" t="s">
         <v>9</v>
       </c>
       <c r="F57" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G57">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58">
-        <v>19330051920121</v>
+        <v>19330051920022</v>
       </c>
       <c r="B58" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C58" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="D58" t="s">
-        <v>159</v>
+        <v>186</v>
       </c>
       <c r="E58" t="s">
         <v>9</v>
       </c>
       <c r="F58" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G58">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59">
-        <v>19330051920122</v>
+        <v>19330051920021</v>
       </c>
       <c r="B59" t="s">
+        <v>67</v>
+      </c>
+      <c r="C59" t="s">
+        <v>120</v>
+      </c>
+      <c r="D59" t="s">
+        <v>187</v>
+      </c>
+      <c r="E59" t="s">
+        <v>9</v>
+      </c>
+      <c r="F59" t="s">
+        <v>11</v>
+      </c>
+      <c r="G59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60">
+        <v>18330061460390</v>
+      </c>
+      <c r="B60" t="s">
+        <v>68</v>
+      </c>
+      <c r="C60" t="s">
+        <v>85</v>
+      </c>
+      <c r="D60" t="s">
+        <v>188</v>
+      </c>
+      <c r="E60" t="s">
+        <v>9</v>
+      </c>
+      <c r="F60" t="s">
+        <v>11</v>
+      </c>
+      <c r="G60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
+      <c r="A61">
+        <v>19330051920025</v>
+      </c>
+      <c r="B61" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" t="s">
+        <v>54</v>
+      </c>
+      <c r="D61" t="s">
+        <v>189</v>
+      </c>
+      <c r="E61" t="s">
+        <v>9</v>
+      </c>
+      <c r="F61" t="s">
+        <v>11</v>
+      </c>
+      <c r="G61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
+      <c r="A62">
+        <v>19330051920029</v>
+      </c>
+      <c r="B62" t="s">
+        <v>51</v>
+      </c>
+      <c r="C62" t="s">
+        <v>67</v>
+      </c>
+      <c r="D62" t="s">
+        <v>190</v>
+      </c>
+      <c r="E62" t="s">
+        <v>9</v>
+      </c>
+      <c r="F62" t="s">
+        <v>11</v>
+      </c>
+      <c r="G62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
+      <c r="A63">
+        <v>19330051920030</v>
+      </c>
+      <c r="B63" t="s">
+        <v>51</v>
+      </c>
+      <c r="C63" t="s">
+        <v>51</v>
+      </c>
+      <c r="D63" t="s">
+        <v>191</v>
+      </c>
+      <c r="E63" t="s">
+        <v>9</v>
+      </c>
+      <c r="F63" t="s">
+        <v>11</v>
+      </c>
+      <c r="G63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
+      <c r="A64">
+        <v>19330051920031</v>
+      </c>
+      <c r="B64" t="s">
         <v>69</v>
       </c>
-      <c r="C59" t="s">
-        <v>103</v>
-      </c>
-      <c r="D59" t="s">
-        <v>160</v>
-      </c>
-      <c r="E59" t="s">
-        <v>9</v>
-      </c>
-      <c r="F59" t="s">
+      <c r="C64" t="s">
+        <v>121</v>
+      </c>
+      <c r="D64" t="s">
+        <v>192</v>
+      </c>
+      <c r="E64" t="s">
+        <v>9</v>
+      </c>
+      <c r="F64" t="s">
+        <v>11</v>
+      </c>
+      <c r="G64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
+      <c r="A65">
+        <v>19330051920035</v>
+      </c>
+      <c r="B65" t="s">
+        <v>70</v>
+      </c>
+      <c r="C65" t="s">
+        <v>51</v>
+      </c>
+      <c r="D65" t="s">
+        <v>193</v>
+      </c>
+      <c r="E65" t="s">
+        <v>9</v>
+      </c>
+      <c r="F65" t="s">
+        <v>11</v>
+      </c>
+      <c r="G65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7">
+      <c r="A66">
+        <v>19330051920148</v>
+      </c>
+      <c r="B66" t="s">
+        <v>71</v>
+      </c>
+      <c r="C66" t="s">
+        <v>122</v>
+      </c>
+      <c r="D66" t="s">
+        <v>194</v>
+      </c>
+      <c r="E66" t="s">
+        <v>9</v>
+      </c>
+      <c r="F66" t="s">
+        <v>12</v>
+      </c>
+      <c r="G66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7">
+      <c r="A67">
+        <v>19330051920153</v>
+      </c>
+      <c r="B67" t="s">
+        <v>23</v>
+      </c>
+      <c r="C67" t="s">
+        <v>123</v>
+      </c>
+      <c r="D67" t="s">
+        <v>195</v>
+      </c>
+      <c r="E67" t="s">
+        <v>9</v>
+      </c>
+      <c r="F67" t="s">
+        <v>12</v>
+      </c>
+      <c r="G67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7">
+      <c r="A68">
+        <v>19330051920152</v>
+      </c>
+      <c r="B68" t="s">
+        <v>72</v>
+      </c>
+      <c r="C68" t="s">
+        <v>27</v>
+      </c>
+      <c r="D68" t="s">
+        <v>196</v>
+      </c>
+      <c r="E68" t="s">
+        <v>9</v>
+      </c>
+      <c r="F68" t="s">
+        <v>12</v>
+      </c>
+      <c r="G68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7">
+      <c r="A69">
+        <v>19330051920151</v>
+      </c>
+      <c r="B69" t="s">
+        <v>73</v>
+      </c>
+      <c r="C69" t="s">
+        <v>37</v>
+      </c>
+      <c r="D69" t="s">
+        <v>197</v>
+      </c>
+      <c r="E69" t="s">
+        <v>9</v>
+      </c>
+      <c r="F69" t="s">
+        <v>12</v>
+      </c>
+      <c r="G69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7">
+      <c r="A70">
+        <v>19330051920160</v>
+      </c>
+      <c r="B70" t="s">
+        <v>37</v>
+      </c>
+      <c r="C70" t="s">
+        <v>44</v>
+      </c>
+      <c r="D70" t="s">
+        <v>198</v>
+      </c>
+      <c r="E70" t="s">
+        <v>9</v>
+      </c>
+      <c r="F70" t="s">
+        <v>12</v>
+      </c>
+      <c r="G70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7">
+      <c r="A71">
+        <v>19330051920423</v>
+      </c>
+      <c r="B71" t="s">
+        <v>55</v>
+      </c>
+      <c r="C71" t="s">
+        <v>124</v>
+      </c>
+      <c r="D71" t="s">
+        <v>199</v>
+      </c>
+      <c r="E71" t="s">
+        <v>9</v>
+      </c>
+      <c r="F71" t="s">
+        <v>12</v>
+      </c>
+      <c r="G71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7">
+      <c r="A72">
+        <v>19330051920281</v>
+      </c>
+      <c r="B72" t="s">
+        <v>55</v>
+      </c>
+      <c r="C72" t="s">
+        <v>83</v>
+      </c>
+      <c r="D72" t="s">
+        <v>200</v>
+      </c>
+      <c r="E72" t="s">
+        <v>9</v>
+      </c>
+      <c r="F72" t="s">
+        <v>12</v>
+      </c>
+      <c r="G72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7">
+      <c r="A73">
+        <v>19330051920163</v>
+      </c>
+      <c r="B73" t="s">
+        <v>74</v>
+      </c>
+      <c r="C73" t="s">
+        <v>51</v>
+      </c>
+      <c r="D73" t="s">
+        <v>201</v>
+      </c>
+      <c r="E73" t="s">
+        <v>9</v>
+      </c>
+      <c r="F73" t="s">
+        <v>12</v>
+      </c>
+      <c r="G73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7">
+      <c r="A74">
+        <v>19330051920156</v>
+      </c>
+      <c r="B74" t="s">
+        <v>47</v>
+      </c>
+      <c r="C74" t="s">
+        <v>51</v>
+      </c>
+      <c r="D74" t="s">
+        <v>202</v>
+      </c>
+      <c r="E74" t="s">
+        <v>9</v>
+      </c>
+      <c r="F74" t="s">
+        <v>12</v>
+      </c>
+      <c r="G74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7">
+      <c r="A75">
+        <v>19330051920165</v>
+      </c>
+      <c r="B75" t="s">
+        <v>75</v>
+      </c>
+      <c r="C75" t="s">
+        <v>125</v>
+      </c>
+      <c r="D75" t="s">
+        <v>203</v>
+      </c>
+      <c r="E75" t="s">
+        <v>9</v>
+      </c>
+      <c r="F75" t="s">
+        <v>12</v>
+      </c>
+      <c r="G75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7">
+      <c r="A76">
+        <v>19330051920166</v>
+      </c>
+      <c r="B76" t="s">
+        <v>76</v>
+      </c>
+      <c r="C76" t="s">
+        <v>69</v>
+      </c>
+      <c r="D76" t="s">
+        <v>204</v>
+      </c>
+      <c r="E76" t="s">
+        <v>9</v>
+      </c>
+      <c r="F76" t="s">
+        <v>12</v>
+      </c>
+      <c r="G76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7">
+      <c r="A77">
+        <v>19330051920170</v>
+      </c>
+      <c r="B77" t="s">
+        <v>77</v>
+      </c>
+      <c r="C77" t="s">
+        <v>83</v>
+      </c>
+      <c r="D77" t="s">
+        <v>205</v>
+      </c>
+      <c r="E77" t="s">
+        <v>9</v>
+      </c>
+      <c r="F77" t="s">
+        <v>12</v>
+      </c>
+      <c r="G77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7">
+      <c r="A78">
+        <v>19330051920172</v>
+      </c>
+      <c r="B78" t="s">
+        <v>78</v>
+      </c>
+      <c r="C78" t="s">
+        <v>122</v>
+      </c>
+      <c r="D78" t="s">
+        <v>206</v>
+      </c>
+      <c r="E78" t="s">
+        <v>9</v>
+      </c>
+      <c r="F78" t="s">
+        <v>12</v>
+      </c>
+      <c r="G78">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7">
+      <c r="A79">
+        <v>19330051920173</v>
+      </c>
+      <c r="B79" t="s">
+        <v>79</v>
+      </c>
+      <c r="C79" t="s">
+        <v>126</v>
+      </c>
+      <c r="D79" t="s">
+        <v>207</v>
+      </c>
+      <c r="E79" t="s">
+        <v>9</v>
+      </c>
+      <c r="F79" t="s">
+        <v>12</v>
+      </c>
+      <c r="G79">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7">
+      <c r="A80">
+        <v>19330051920174</v>
+      </c>
+      <c r="B80" t="s">
+        <v>51</v>
+      </c>
+      <c r="C80" t="s">
+        <v>29</v>
+      </c>
+      <c r="D80" t="s">
+        <v>134</v>
+      </c>
+      <c r="E80" t="s">
+        <v>9</v>
+      </c>
+      <c r="F80" t="s">
+        <v>12</v>
+      </c>
+      <c r="G80">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7">
+      <c r="A81">
+        <v>19330051920175</v>
+      </c>
+      <c r="B81" t="s">
+        <v>51</v>
+      </c>
+      <c r="C81" t="s">
+        <v>80</v>
+      </c>
+      <c r="D81" t="s">
+        <v>208</v>
+      </c>
+      <c r="E81" t="s">
+        <v>9</v>
+      </c>
+      <c r="F81" t="s">
+        <v>12</v>
+      </c>
+      <c r="G81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7">
+      <c r="A82">
+        <v>19330051920179</v>
+      </c>
+      <c r="B82" t="s">
+        <v>32</v>
+      </c>
+      <c r="C82" t="s">
+        <v>37</v>
+      </c>
+      <c r="D82" t="s">
+        <v>209</v>
+      </c>
+      <c r="E82" t="s">
+        <v>9</v>
+      </c>
+      <c r="F82" t="s">
+        <v>12</v>
+      </c>
+      <c r="G82">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7">
+      <c r="A83">
+        <v>19330051920180</v>
+      </c>
+      <c r="B83" t="s">
+        <v>32</v>
+      </c>
+      <c r="C83" t="s">
+        <v>127</v>
+      </c>
+      <c r="D83" t="s">
+        <v>210</v>
+      </c>
+      <c r="E83" t="s">
+        <v>9</v>
+      </c>
+      <c r="F83" t="s">
+        <v>12</v>
+      </c>
+      <c r="G83">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7">
+      <c r="A84">
+        <v>19330051920182</v>
+      </c>
+      <c r="B84" t="s">
+        <v>80</v>
+      </c>
+      <c r="C84" t="s">
+        <v>128</v>
+      </c>
+      <c r="D84" t="s">
+        <v>211</v>
+      </c>
+      <c r="E84" t="s">
+        <v>9</v>
+      </c>
+      <c r="F84" t="s">
+        <v>12</v>
+      </c>
+      <c r="G84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7">
+      <c r="A85">
+        <v>19330051920430</v>
+      </c>
+      <c r="B85" t="s">
+        <v>81</v>
+      </c>
+      <c r="C85" t="s">
+        <v>79</v>
+      </c>
+      <c r="D85" t="s">
+        <v>212</v>
+      </c>
+      <c r="E85" t="s">
+        <v>9</v>
+      </c>
+      <c r="F85" t="s">
+        <v>13</v>
+      </c>
+      <c r="G85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7">
+      <c r="A86">
+        <v>19330051920234</v>
+      </c>
+      <c r="B86" t="s">
+        <v>82</v>
+      </c>
+      <c r="C86" t="s">
+        <v>129</v>
+      </c>
+      <c r="D86" t="s">
+        <v>213</v>
+      </c>
+      <c r="E86" t="s">
+        <v>9</v>
+      </c>
+      <c r="F86" t="s">
+        <v>13</v>
+      </c>
+      <c r="G86">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7">
+      <c r="A87">
+        <v>19330051920429</v>
+      </c>
+      <c r="B87" t="s">
+        <v>83</v>
+      </c>
+      <c r="C87" t="s">
+        <v>130</v>
+      </c>
+      <c r="D87" t="s">
+        <v>214</v>
+      </c>
+      <c r="E87" t="s">
+        <v>9</v>
+      </c>
+      <c r="F87" t="s">
+        <v>13</v>
+      </c>
+      <c r="G87">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7">
+      <c r="A88">
+        <v>19330051920084</v>
+      </c>
+      <c r="B88" t="s">
+        <v>84</v>
+      </c>
+      <c r="C88" t="s">
+        <v>131</v>
+      </c>
+      <c r="D88" t="s">
+        <v>215</v>
+      </c>
+      <c r="E88" t="s">
+        <v>9</v>
+      </c>
+      <c r="F88" t="s">
         <v>14</v>
       </c>
-      <c r="G59">
-        <v>2</v>
+      <c r="G88">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7">
+      <c r="A89">
+        <v>19330051920090</v>
+      </c>
+      <c r="B89" t="s">
+        <v>85</v>
+      </c>
+      <c r="C89" t="s">
+        <v>59</v>
+      </c>
+      <c r="D89" t="s">
+        <v>216</v>
+      </c>
+      <c r="E89" t="s">
+        <v>9</v>
+      </c>
+      <c r="F89" t="s">
+        <v>14</v>
+      </c>
+      <c r="G89">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7">
+      <c r="A90">
+        <v>19330051920089</v>
+      </c>
+      <c r="B90" t="s">
+        <v>85</v>
+      </c>
+      <c r="C90" t="s">
+        <v>59</v>
+      </c>
+      <c r="D90" t="s">
+        <v>217</v>
+      </c>
+      <c r="E90" t="s">
+        <v>9</v>
+      </c>
+      <c r="F90" t="s">
+        <v>14</v>
+      </c>
+      <c r="G90">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7">
+      <c r="A91">
+        <v>19330051920107</v>
+      </c>
+      <c r="B91" t="s">
+        <v>86</v>
+      </c>
+      <c r="C91" t="s">
+        <v>132</v>
+      </c>
+      <c r="D91" t="s">
+        <v>218</v>
+      </c>
+      <c r="E91" t="s">
+        <v>9</v>
+      </c>
+      <c r="F91" t="s">
+        <v>14</v>
+      </c>
+      <c r="G91">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7">
+      <c r="A92">
+        <v>19330051920121</v>
+      </c>
+      <c r="B92" t="s">
+        <v>87</v>
+      </c>
+      <c r="C92" t="s">
+        <v>133</v>
+      </c>
+      <c r="D92" t="s">
+        <v>219</v>
+      </c>
+      <c r="E92" t="s">
+        <v>9</v>
+      </c>
+      <c r="F92" t="s">
+        <v>14</v>
+      </c>
+      <c r="G92">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Velasco Sánchez David - Estadisticos 20212.xlsx
+++ b/docentes/Velasco Sánchez David - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="89">
   <si>
     <t>Mat</t>
   </si>
@@ -88,108 +88,111 @@
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>DE LUNA</t>
+  </si>
+  <si>
     <t>OJEDA</t>
   </si>
   <si>
     <t>DE JESUS</t>
   </si>
   <si>
+    <t>ROMAN</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>COUDER</t>
+  </si>
+  <si>
+    <t>MIXCOAC</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>ZUÑIGA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
+    <t>TAPIA</t>
+  </si>
+  <si>
     <t>RIOS</t>
   </si>
   <si>
-    <t>COUDER</t>
-  </si>
-  <si>
-    <t>MIXCOAC</t>
-  </si>
-  <si>
-    <t>ZUÑIGA</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>CLEMENTE</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>CARRASCO</t>
+  </si>
+  <si>
+    <t>CORDOVA</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>SORIANO</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>CHICO</t>
   </si>
   <si>
     <t>MORALES</t>
   </si>
   <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>SUAREZ</t>
-  </si>
-  <si>
-    <t>TAPIA</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>CARRASCO</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>SORIANO</t>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>GARATE</t>
+  </si>
+  <si>
+    <t>AVELINO</t>
+  </si>
+  <si>
+    <t>DEL ANGEL</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
   </si>
   <si>
     <t>CHAVEZ</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>GARATE</t>
-  </si>
-  <si>
-    <t>AVELINO</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>CHICO</t>
-  </si>
-  <si>
     <t>ONOFRE</t>
   </si>
   <si>
@@ -205,15 +208,15 @@
     <t>ANGUIANO</t>
   </si>
   <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
     <t>ELIAS ALONSO</t>
   </si>
   <si>
     <t>KARLA RENATA</t>
   </si>
   <si>
+    <t>EUDY</t>
+  </si>
+  <si>
     <t>KAREN YAZMIN</t>
   </si>
   <si>
@@ -223,64 +226,64 @@
     <t>JESUS</t>
   </si>
   <si>
+    <t>NATANAEL</t>
+  </si>
+  <si>
+    <t>ERICK ORLANDO</t>
+  </si>
+  <si>
+    <t>YULIANA</t>
+  </si>
+  <si>
+    <t>ELYDEN JULYSSA</t>
+  </si>
+  <si>
+    <t>ABRIL CITLALLI</t>
+  </si>
+  <si>
+    <t>MARLENE</t>
+  </si>
+  <si>
+    <t>DANIELA JAQUELINE</t>
+  </si>
+  <si>
+    <t>JOSUE</t>
+  </si>
+  <si>
+    <t>AXEL</t>
+  </si>
+  <si>
+    <t>URIEL</t>
+  </si>
+  <si>
+    <t>ROMARIO ALDAIR</t>
+  </si>
+  <si>
+    <t>YAMILET</t>
+  </si>
+  <si>
+    <t>MARIA ISABEL</t>
+  </si>
+  <si>
     <t>JOSE AUGUSTO</t>
   </si>
   <si>
-    <t>YULIANA</t>
-  </si>
-  <si>
-    <t>ELYDEN JULYSSA</t>
-  </si>
-  <si>
-    <t>MARLENE</t>
-  </si>
-  <si>
-    <t>DANIELA JAQUELINE</t>
-  </si>
-  <si>
-    <t>ELEAZAR RIGOBERTO</t>
-  </si>
-  <si>
-    <t>JOSUE</t>
-  </si>
-  <si>
-    <t>AXEL</t>
-  </si>
-  <si>
-    <t>JOSE ALONSO</t>
+    <t>MARIANA JOSELIN</t>
+  </si>
+  <si>
+    <t>KATHERINE AZUL</t>
+  </si>
+  <si>
+    <t>RUTH</t>
+  </si>
+  <si>
+    <t>YARELY JACQUELINE</t>
+  </si>
+  <si>
+    <t>YESUA ISIDRO</t>
   </si>
   <si>
     <t>YARITZI</t>
-  </si>
-  <si>
-    <t>ROMARIO ALDAIR</t>
-  </si>
-  <si>
-    <t>NATANAEL</t>
-  </si>
-  <si>
-    <t>ERICK ORLANDO</t>
-  </si>
-  <si>
-    <t>MARIANA JOSELIN</t>
-  </si>
-  <si>
-    <t>KATHERINE AZUL</t>
-  </si>
-  <si>
-    <t>RUTH</t>
-  </si>
-  <si>
-    <t>YARELY JACQUELINE</t>
-  </si>
-  <si>
-    <t>YESUA ISIDRO</t>
-  </si>
-  <si>
-    <t>YAMILET</t>
-  </si>
-  <si>
-    <t>MARIA ISABEL</t>
   </si>
 </sst>
 </file>
@@ -730,10 +733,10 @@
         <v>12</v>
       </c>
       <c r="C4">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -742,7 +745,7 @@
         <v>27</v>
       </c>
       <c r="G4">
-        <v>77.14</v>
+        <v>79.41</v>
       </c>
       <c r="H4">
         <v>9.300000000000001</v>
@@ -893,10 +896,10 @@
         <v>12</v>
       </c>
       <c r="C4">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D4">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E4">
         <v>27</v>
@@ -1053,10 +1056,10 @@
         <v>12</v>
       </c>
       <c r="C4">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -1065,7 +1068,7 @@
         <v>27</v>
       </c>
       <c r="G4">
-        <v>77.14</v>
+        <v>79.41</v>
       </c>
       <c r="H4">
         <v>9.300000000000001</v>
@@ -1130,7 +1133,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1208,7 +1211,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920276</v>
+        <v>19220030050208</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
@@ -1231,7 +1234,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920012</v>
+        <v>20330051920276</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
@@ -1243,10 +1246,10 @@
         <v>66</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1254,10 +1257,10 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920010</v>
+        <v>19330051920012</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s">
         <v>47</v>
@@ -1277,7 +1280,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920023</v>
+        <v>19330051920010</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
@@ -1300,7 +1303,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920276</v>
+        <v>18330061460390</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
@@ -1315,7 +1318,7 @@
         <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1323,13 +1326,13 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920168</v>
+        <v>19330051920038</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="D9" t="s">
         <v>70</v>
@@ -1338,7 +1341,7 @@
         <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1346,13 +1349,13 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920183</v>
+        <v>19330051920276</v>
       </c>
       <c r="B10" t="s">
         <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="D10" t="s">
         <v>71</v>
@@ -1369,13 +1372,13 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>19330051920244</v>
+        <v>19330051920168</v>
       </c>
       <c r="B11" t="s">
         <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D11" t="s">
         <v>72</v>
@@ -1384,7 +1387,7 @@
         <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1392,7 +1395,7 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>19330051920092</v>
+        <v>19330051920176</v>
       </c>
       <c r="B12" t="s">
         <v>30</v>
@@ -1407,7 +1410,7 @@
         <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -1415,7 +1418,7 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>19330051920094</v>
+        <v>19330051920183</v>
       </c>
       <c r="B13" t="s">
         <v>31</v>
@@ -1430,7 +1433,7 @@
         <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G13">
         <v>2</v>
@@ -1438,13 +1441,13 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>19330051920105</v>
+        <v>19330051920244</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="D14" t="s">
         <v>75</v>
@@ -1453,7 +1456,7 @@
         <v>9</v>
       </c>
       <c r="F14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G14">
         <v>2</v>
@@ -1461,13 +1464,13 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>19330051920112</v>
+        <v>19330051920094</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D15" t="s">
         <v>76</v>
@@ -1484,13 +1487,13 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>19330051920117</v>
+        <v>19330051920105</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C16" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="D16" t="s">
         <v>77</v>
@@ -1507,13 +1510,13 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>19330051920118</v>
+        <v>19330051920103</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="C17" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="D17" t="s">
         <v>78</v>
@@ -1530,13 +1533,13 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>18330061460390</v>
+        <v>19330051920118</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C18" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="D18" t="s">
         <v>79</v>
@@ -1545,21 +1548,21 @@
         <v>9</v>
       </c>
       <c r="F18" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G18">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>19330051920038</v>
+        <v>19330051920119</v>
       </c>
       <c r="B19" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C19" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="D19" t="s">
         <v>80</v>
@@ -1568,21 +1571,21 @@
         <v>9</v>
       </c>
       <c r="F19" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G19">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>19330051920281</v>
+        <v>19330051920120</v>
       </c>
       <c r="B20" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C20" t="s">
-        <v>21</v>
+        <v>56</v>
       </c>
       <c r="D20" t="s">
         <v>81</v>
@@ -1591,18 +1594,18 @@
         <v>9</v>
       </c>
       <c r="F20" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G20">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>19330051920173</v>
+        <v>19330051920023</v>
       </c>
       <c r="B21" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C21" t="s">
         <v>57</v>
@@ -1614,7 +1617,7 @@
         <v>9</v>
       </c>
       <c r="F21" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -1622,13 +1625,13 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>19330051920180</v>
+        <v>19330051920281</v>
       </c>
       <c r="B22" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="C22" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="D22" t="s">
         <v>83</v>
@@ -1645,13 +1648,13 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>19330051920429</v>
+        <v>19330051920173</v>
       </c>
       <c r="B23" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="C23" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D23" t="s">
         <v>84</v>
@@ -1660,7 +1663,7 @@
         <v>9</v>
       </c>
       <c r="F23" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -1668,13 +1671,13 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>19330051920245</v>
+        <v>19330051920180</v>
       </c>
       <c r="B24" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="C24" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D24" t="s">
         <v>85</v>
@@ -1683,7 +1686,7 @@
         <v>9</v>
       </c>
       <c r="F24" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1691,22 +1694,22 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>19330051920116</v>
+        <v>19330051920429</v>
       </c>
       <c r="B25" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="C25" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D25" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="E25" t="s">
         <v>9</v>
       </c>
       <c r="F25" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -1714,22 +1717,22 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>19330051920119</v>
+        <v>19330051920245</v>
       </c>
       <c r="B26" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C26" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="D26" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E26" t="s">
         <v>9</v>
       </c>
       <c r="F26" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -1737,16 +1740,16 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>19330051920120</v>
+        <v>19330051920116</v>
       </c>
       <c r="B27" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C27" t="s">
         <v>62</v>
       </c>
       <c r="D27" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="E27" t="s">
         <v>9</v>
@@ -1755,6 +1758,29 @@
         <v>14</v>
       </c>
       <c r="G27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>19330051920117</v>
+      </c>
+      <c r="B28" t="s">
+        <v>42</v>
+      </c>
+      <c r="C28" t="s">
+        <v>32</v>
+      </c>
+      <c r="D28" t="s">
+        <v>88</v>
+      </c>
+      <c r="E28" t="s">
+        <v>9</v>
+      </c>
+      <c r="F28" t="s">
+        <v>14</v>
+      </c>
+      <c r="G28">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Velasco Sánchez David - Estadisticos 20212.xlsx
+++ b/docentes/Velasco Sánchez David - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="51">
   <si>
     <t>Mat</t>
   </si>
@@ -97,117 +97,48 @@
     <t>DE JESUS</t>
   </si>
   <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
     <t>COUDER</t>
   </si>
   <si>
     <t>MIXCOAC</t>
   </si>
   <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>CARRASCO</t>
+  </si>
+  <si>
+    <t>CORDOVA</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>SORIANO</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>ZUÑIGA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>SUAREZ</t>
-  </si>
-  <si>
-    <t>TAPIA</t>
-  </si>
-  <si>
-    <t>RIOS</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>CARRASCO</t>
-  </si>
-  <si>
-    <t>CORDOVA</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>SORIANO</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>CHICO</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
     <t>GARATE</t>
   </si>
   <si>
     <t>AVELINO</t>
   </si>
   <si>
-    <t>DEL ANGEL</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>CHAVEZ</t>
-  </si>
-  <si>
-    <t>ONOFRE</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>CALPULALPAN</t>
-  </si>
-  <si>
-    <t>LLAVE</t>
-  </si>
-  <si>
-    <t>ANGUIANO</t>
-  </si>
-  <si>
     <t>ELIAS ALONSO</t>
   </si>
   <si>
@@ -220,70 +151,25 @@
     <t>KAREN YAZMIN</t>
   </si>
   <si>
-    <t>EMMANUEL</t>
-  </si>
-  <si>
     <t>JESUS</t>
   </si>
   <si>
-    <t>NATANAEL</t>
-  </si>
-  <si>
-    <t>ERICK ORLANDO</t>
-  </si>
-  <si>
     <t>YULIANA</t>
   </si>
   <si>
     <t>ELYDEN JULYSSA</t>
   </si>
   <si>
-    <t>ABRIL CITLALLI</t>
-  </si>
-  <si>
-    <t>MARLENE</t>
-  </si>
-  <si>
-    <t>DANIELA JAQUELINE</t>
-  </si>
-  <si>
     <t>JOSUE</t>
   </si>
   <si>
     <t>AXEL</t>
   </si>
   <si>
-    <t>URIEL</t>
-  </si>
-  <si>
     <t>ROMARIO ALDAIR</t>
   </si>
   <si>
     <t>YAMILET</t>
-  </si>
-  <si>
-    <t>MARIA ISABEL</t>
-  </si>
-  <si>
-    <t>JOSE AUGUSTO</t>
-  </si>
-  <si>
-    <t>MARIANA JOSELIN</t>
-  </si>
-  <si>
-    <t>KATHERINE AZUL</t>
-  </si>
-  <si>
-    <t>RUTH</t>
-  </si>
-  <si>
-    <t>YARELY JACQUELINE</t>
-  </si>
-  <si>
-    <t>YESUA ISIDRO</t>
-  </si>
-  <si>
-    <t>YARITZI</t>
   </si>
 </sst>
 </file>
@@ -710,19 +596,19 @@
         <v>38</v>
       </c>
       <c r="D3">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G3">
-        <v>65.79000000000001</v>
+        <v>78.95</v>
       </c>
       <c r="H3">
-        <v>9.1</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -736,19 +622,19 @@
         <v>34</v>
       </c>
       <c r="D4">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G4">
-        <v>79.41</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="H4">
-        <v>9.300000000000001</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -762,19 +648,19 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G5">
-        <v>70.83</v>
+        <v>79.17</v>
       </c>
       <c r="H5">
-        <v>8.1</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -788,19 +674,19 @@
         <v>31</v>
       </c>
       <c r="D6">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F6">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G6">
-        <v>51.61</v>
+        <v>67.73999999999999</v>
       </c>
       <c r="H6">
-        <v>8.5</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -876,16 +762,19 @@
         <v>38</v>
       </c>
       <c r="D3">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="E3">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>73.68000000000001</v>
+      </c>
+      <c r="H3">
+        <v>8.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -899,16 +788,19 @@
         <v>34</v>
       </c>
       <c r="D4">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="E4">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>88.23999999999999</v>
+      </c>
+      <c r="H4">
+        <v>8.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -922,16 +814,19 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="E5">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>91.67</v>
+      </c>
+      <c r="H5">
+        <v>7.5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -945,16 +840,19 @@
         <v>31</v>
       </c>
       <c r="D6">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="E6">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>64.52</v>
+      </c>
+      <c r="H6">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1033,19 +931,19 @@
         <v>38</v>
       </c>
       <c r="D3">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G3">
-        <v>65.79000000000001</v>
+        <v>78.95</v>
       </c>
       <c r="H3">
-        <v>9.1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1059,19 +957,19 @@
         <v>34</v>
       </c>
       <c r="D4">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="G4">
-        <v>79.41</v>
+        <v>94.12</v>
       </c>
       <c r="H4">
-        <v>9.300000000000001</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1085,19 +983,19 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G5">
-        <v>70.83</v>
+        <v>91.67</v>
       </c>
       <c r="H5">
-        <v>8.1</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1111,19 +1009,19 @@
         <v>31</v>
       </c>
       <c r="D6">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F6">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G6">
-        <v>51.61</v>
+        <v>67.73999999999999</v>
       </c>
       <c r="H6">
-        <v>8.5</v>
+        <v>7.4</v>
       </c>
     </row>
   </sheetData>
@@ -1133,7 +1031,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1171,10 +1069,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="D2" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1194,10 +1092,10 @@
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D3" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1217,10 +1115,10 @@
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1240,10 +1138,10 @@
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="D5" t="s">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1257,16 +1155,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920012</v>
+        <v>19330051920010</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -1280,22 +1178,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920010</v>
+        <v>19330051920276</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1303,22 +1201,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>18330061460390</v>
+        <v>19330051920168</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="D8" t="s">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1326,22 +1224,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920038</v>
+        <v>19330051920094</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="D9" t="s">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1349,22 +1247,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920276</v>
+        <v>19330051920105</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="D10" t="s">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1372,22 +1270,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>19330051920168</v>
+        <v>19330051920118</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D11" t="s">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1395,393 +1293,25 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>19330051920176</v>
+        <v>19330051920119</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="D12" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G12">
         <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>19330051920183</v>
-      </c>
-      <c r="B13" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" t="s">
-        <v>52</v>
-      </c>
-      <c r="D13" t="s">
-        <v>74</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" t="s">
-        <v>12</v>
-      </c>
-      <c r="G13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>19330051920244</v>
-      </c>
-      <c r="B14" t="s">
-        <v>27</v>
-      </c>
-      <c r="C14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D14" t="s">
-        <v>75</v>
-      </c>
-      <c r="E14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" t="s">
-        <v>13</v>
-      </c>
-      <c r="G14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>19330051920094</v>
-      </c>
-      <c r="B15" t="s">
-        <v>32</v>
-      </c>
-      <c r="C15" t="s">
-        <v>53</v>
-      </c>
-      <c r="D15" t="s">
-        <v>76</v>
-      </c>
-      <c r="E15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" t="s">
-        <v>14</v>
-      </c>
-      <c r="G15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>19330051920105</v>
-      </c>
-      <c r="B16" t="s">
-        <v>33</v>
-      </c>
-      <c r="C16" t="s">
-        <v>54</v>
-      </c>
-      <c r="D16" t="s">
-        <v>77</v>
-      </c>
-      <c r="E16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" t="s">
-        <v>14</v>
-      </c>
-      <c r="G16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>19330051920103</v>
-      </c>
-      <c r="B17" t="s">
-        <v>21</v>
-      </c>
-      <c r="C17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D17" t="s">
-        <v>78</v>
-      </c>
-      <c r="E17" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" t="s">
-        <v>14</v>
-      </c>
-      <c r="G17">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>19330051920118</v>
-      </c>
-      <c r="B18" t="s">
-        <v>34</v>
-      </c>
-      <c r="C18" t="s">
-        <v>21</v>
-      </c>
-      <c r="D18" t="s">
-        <v>79</v>
-      </c>
-      <c r="E18" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" t="s">
-        <v>14</v>
-      </c>
-      <c r="G18">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>19330051920119</v>
-      </c>
-      <c r="B19" t="s">
-        <v>35</v>
-      </c>
-      <c r="C19" t="s">
-        <v>25</v>
-      </c>
-      <c r="D19" t="s">
-        <v>80</v>
-      </c>
-      <c r="E19" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" t="s">
-        <v>14</v>
-      </c>
-      <c r="G19">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>19330051920120</v>
-      </c>
-      <c r="B20" t="s">
-        <v>36</v>
-      </c>
-      <c r="C20" t="s">
-        <v>56</v>
-      </c>
-      <c r="D20" t="s">
-        <v>81</v>
-      </c>
-      <c r="E20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" t="s">
-        <v>14</v>
-      </c>
-      <c r="G20">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>19330051920023</v>
-      </c>
-      <c r="B21" t="s">
-        <v>37</v>
-      </c>
-      <c r="C21" t="s">
-        <v>57</v>
-      </c>
-      <c r="D21" t="s">
-        <v>82</v>
-      </c>
-      <c r="E21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" t="s">
-        <v>11</v>
-      </c>
-      <c r="G21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>19330051920281</v>
-      </c>
-      <c r="B22" t="s">
-        <v>38</v>
-      </c>
-      <c r="C22" t="s">
-        <v>21</v>
-      </c>
-      <c r="D22" t="s">
-        <v>83</v>
-      </c>
-      <c r="E22" t="s">
-        <v>9</v>
-      </c>
-      <c r="F22" t="s">
-        <v>12</v>
-      </c>
-      <c r="G22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>19330051920173</v>
-      </c>
-      <c r="B23" t="s">
-        <v>39</v>
-      </c>
-      <c r="C23" t="s">
-        <v>58</v>
-      </c>
-      <c r="D23" t="s">
-        <v>84</v>
-      </c>
-      <c r="E23" t="s">
-        <v>9</v>
-      </c>
-      <c r="F23" t="s">
-        <v>12</v>
-      </c>
-      <c r="G23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>19330051920180</v>
-      </c>
-      <c r="B24" t="s">
-        <v>27</v>
-      </c>
-      <c r="C24" t="s">
-        <v>59</v>
-      </c>
-      <c r="D24" t="s">
-        <v>85</v>
-      </c>
-      <c r="E24" t="s">
-        <v>9</v>
-      </c>
-      <c r="F24" t="s">
-        <v>12</v>
-      </c>
-      <c r="G24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>19330051920429</v>
-      </c>
-      <c r="B25" t="s">
-        <v>21</v>
-      </c>
-      <c r="C25" t="s">
-        <v>60</v>
-      </c>
-      <c r="D25" t="s">
-        <v>86</v>
-      </c>
-      <c r="E25" t="s">
-        <v>9</v>
-      </c>
-      <c r="F25" t="s">
-        <v>13</v>
-      </c>
-      <c r="G25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>19330051920245</v>
-      </c>
-      <c r="B26" t="s">
-        <v>40</v>
-      </c>
-      <c r="C26" t="s">
-        <v>61</v>
-      </c>
-      <c r="D26" t="s">
-        <v>87</v>
-      </c>
-      <c r="E26" t="s">
-        <v>9</v>
-      </c>
-      <c r="F26" t="s">
-        <v>13</v>
-      </c>
-      <c r="G26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>19330051920116</v>
-      </c>
-      <c r="B27" t="s">
-        <v>41</v>
-      </c>
-      <c r="C27" t="s">
-        <v>62</v>
-      </c>
-      <c r="D27" t="s">
-        <v>76</v>
-      </c>
-      <c r="E27" t="s">
-        <v>9</v>
-      </c>
-      <c r="F27" t="s">
-        <v>14</v>
-      </c>
-      <c r="G27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>19330051920117</v>
-      </c>
-      <c r="B28" t="s">
-        <v>42</v>
-      </c>
-      <c r="C28" t="s">
-        <v>32</v>
-      </c>
-      <c r="D28" t="s">
-        <v>88</v>
-      </c>
-      <c r="E28" t="s">
-        <v>9</v>
-      </c>
-      <c r="F28" t="s">
-        <v>14</v>
-      </c>
-      <c r="G28">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Velasco Sánchez David - Estadisticos 20212.xlsx
+++ b/docentes/Velasco Sánchez David - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="40">
   <si>
     <t>Mat</t>
   </si>
@@ -82,73 +82,40 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>COUDER</t>
+  </si>
+  <si>
+    <t>MIXCOAC</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
+    <t>SORIANO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>GARATE</t>
+  </si>
+  <si>
+    <t>AVELINO</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>DE LUNA</t>
-  </si>
-  <si>
-    <t>OJEDA</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>COUDER</t>
-  </si>
-  <si>
-    <t>MIXCOAC</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>SUAREZ</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>CARRASCO</t>
-  </si>
-  <si>
-    <t>CORDOVA</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>SORIANO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>GARATE</t>
-  </si>
-  <si>
-    <t>AVELINO</t>
-  </si>
-  <si>
-    <t>ELIAS ALONSO</t>
-  </si>
-  <si>
-    <t>KARLA RENATA</t>
-  </si>
-  <si>
-    <t>EUDY</t>
-  </si>
-  <si>
-    <t>KAREN YAZMIN</t>
   </si>
   <si>
     <t>JESUS</t>
@@ -570,10 +537,10 @@
         <v>20</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
         <v>10</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
       </c>
       <c r="F2">
         <v>10</v>
@@ -582,7 +549,7 @@
         <v>50</v>
       </c>
       <c r="H2">
-        <v>7.2</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -739,16 +706,19 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E2">
         <v>10</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="H2">
+        <v>6.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -905,19 +875,19 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G2">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="H2">
-        <v>7.2</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1031,7 +1001,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1063,22 +1033,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920270</v>
+        <v>19330051920010</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1086,22 +1056,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920271</v>
+        <v>19330051920276</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1109,22 +1079,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19220030050208</v>
+        <v>19330051920168</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1132,22 +1102,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920276</v>
+        <v>19330051920094</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1155,22 +1125,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920010</v>
+        <v>19330051920105</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D6" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1178,22 +1148,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920276</v>
+        <v>19330051920118</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D7" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1201,116 +1171,24 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920168</v>
+        <v>19330051920119</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>19330051920094</v>
-      </c>
-      <c r="B9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" t="s">
-        <v>47</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>19330051920105</v>
-      </c>
-      <c r="B10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" t="s">
-        <v>39</v>
-      </c>
-      <c r="D10" t="s">
-        <v>48</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>19330051920118</v>
-      </c>
-      <c r="B11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" t="s">
-        <v>21</v>
-      </c>
-      <c r="D11" t="s">
-        <v>49</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>19330051920119</v>
-      </c>
-      <c r="B12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" t="s">
-        <v>25</v>
-      </c>
-      <c r="D12" t="s">
-        <v>50</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>14</v>
-      </c>
-      <c r="G12">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Velasco Sánchez David - Estadisticos 20212.xlsx
+++ b/docentes/Velasco Sánchez David - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="29">
   <si>
     <t>Mat</t>
   </si>
@@ -82,61 +82,28 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>TEPOLE</t>
+  </si>
+  <si>
     <t>DE JESUS</t>
   </si>
   <si>
-    <t>COUDER</t>
-  </si>
-  <si>
     <t>MIXCOAC</t>
   </si>
   <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>SUAREZ</t>
+    <t>MUÑOZ</t>
   </si>
   <si>
     <t>SORIANO</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>GARATE</t>
-  </si>
-  <si>
-    <t>AVELINO</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
+    <t>JOHNNY</t>
   </si>
   <si>
     <t>JESUS</t>
   </si>
   <si>
-    <t>YULIANA</t>
-  </si>
-  <si>
     <t>ELYDEN JULYSSA</t>
-  </si>
-  <si>
-    <t>JOSUE</t>
-  </si>
-  <si>
-    <t>AXEL</t>
-  </si>
-  <si>
-    <t>ROMARIO ALDAIR</t>
-  </si>
-  <si>
-    <t>YAMILET</t>
   </si>
 </sst>
 </file>
@@ -706,19 +673,19 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G2">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="H2">
-        <v>6.4</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -732,19 +699,19 @@
         <v>38</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G3">
-        <v>73.68000000000001</v>
+        <v>78.95</v>
       </c>
       <c r="H3">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -758,19 +725,19 @@
         <v>34</v>
       </c>
       <c r="D4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G4">
-        <v>88.23999999999999</v>
+        <v>94.12</v>
       </c>
       <c r="H4">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -784,7 +751,7 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>2</v>
@@ -796,7 +763,7 @@
         <v>91.67</v>
       </c>
       <c r="H5">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -810,19 +777,19 @@
         <v>31</v>
       </c>
       <c r="D6">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F6">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G6">
-        <v>64.52</v>
+        <v>77.42</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -878,16 +845,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G2">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H2">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -930,16 +897,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G4">
-        <v>94.12</v>
+        <v>97.06</v>
       </c>
       <c r="H4">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -956,13 +923,13 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G5">
-        <v>91.67</v>
+        <v>95.83</v>
       </c>
       <c r="H5">
         <v>7.7</v>
@@ -982,16 +949,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="G6">
-        <v>67.73999999999999</v>
+        <v>100</v>
       </c>
       <c r="H6">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
     </row>
   </sheetData>
@@ -1001,7 +968,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1033,16 +1000,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920010</v>
+        <v>19330051920034</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -1056,25 +1023,25 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920276</v>
+        <v>19330051920010</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1085,10 +1052,10 @@
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -1097,99 +1064,7 @@
         <v>12</v>
       </c>
       <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>19330051920094</v>
-      </c>
-      <c r="B5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>19330051920105</v>
-      </c>
-      <c r="B6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>19330051920118</v>
-      </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>19330051920119</v>
-      </c>
-      <c r="B8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" t="s">
-        <v>39</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Velasco Sánchez David - Estadisticos 20212.xlsx
+++ b/docentes/Velasco Sánchez David - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="27">
   <si>
     <t>Mat</t>
   </si>
@@ -85,22 +85,16 @@
     <t>TEPOLE</t>
   </si>
   <si>
+    <t>MIXCOAC</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
     <t>DE JESUS</t>
   </si>
   <si>
-    <t>MIXCOAC</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>SORIANO</t>
-  </si>
-  <si>
     <t>JOHNNY</t>
-  </si>
-  <si>
-    <t>JESUS</t>
   </si>
   <si>
     <t>ELYDEN JULYSSA</t>
@@ -871,16 +865,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G3">
-        <v>78.95</v>
+        <v>86.84</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -968,7 +962,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1006,10 +1000,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -1023,47 +1017,24 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920010</v>
+        <v>19330051920168</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>19330051920168</v>
-      </c>
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Velasco Sánchez David - Estadisticos 20212.xlsx
+++ b/docentes/Velasco Sánchez David - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="24">
   <si>
     <t>Mat</t>
   </si>
@@ -82,19 +82,10 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>TEPOLE</t>
-  </si>
-  <si>
     <t>MIXCOAC</t>
   </si>
   <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
     <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>JOHNNY</t>
   </si>
   <si>
     <t>ELYDEN JULYSSA</t>
@@ -865,13 +856,13 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G3">
-        <v>86.84</v>
+        <v>92.11</v>
       </c>
       <c r="H3">
         <v>8.1</v>
@@ -962,7 +953,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -994,47 +985,24 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920034</v>
+        <v>19330051920168</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" t="s">
         <v>23</v>
       </c>
-      <c r="D2" t="s">
-        <v>25</v>
-      </c>
       <c r="E2" t="s">
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>19330051920168</v>
-      </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3">
         <v>1</v>
       </c>
     </row>
